--- a/Home/Assets/Quize/1/Quize.xlsx
+++ b/Home/Assets/Quize/1/Quize.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pthorawa\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8FF8B116-C5FD-41D6-99B7-29A6BA2DD048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE231C04-7D82-4855-8454-D75879419E37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="19">
   <si>
     <t>Question</t>
   </si>
@@ -431,8 +431,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="71.26953125" customWidth="1"/>
+    <col min="2" max="2" width="19.81640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
@@ -511,6 +515,546 @@
         <v>10</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31" s="2" t="s">
         <v>2</v>
       </c>
     </row>
